--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_atacama.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_atacama.xlsx
@@ -388,10 +388,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>96.77096056876194</v>
+        <v>96.77096056876195</v>
       </c>
       <c r="C2">
-        <v>18.03429617161641</v>
+        <v>18.03429617161642</v>
       </c>
       <c r="D2">
         <v>64.51374219129492</v>
@@ -413,7 +413,7 @@
         <v>17.04774569945519</v>
       </c>
       <c r="D3">
-        <v>62.44691347432543</v>
+        <v>62.44691347432542</v>
       </c>
       <c r="E3">
         <v>20.50534082621938</v>
@@ -432,7 +432,7 @@
         <v>20.18856629751571</v>
       </c>
       <c r="D4">
-        <v>63.13977850942832</v>
+        <v>63.1397785094283</v>
       </c>
       <c r="E4">
         <v>16.67165519305597</v>
@@ -543,13 +543,13 @@
         <v>136.6203703703704</v>
       </c>
       <c r="C10">
-        <v>16.89083515796059</v>
+        <v>16.89083515796058</v>
       </c>
       <c r="D10">
-        <v>60.03284329058492</v>
+        <v>60.03284329058491</v>
       </c>
       <c r="E10">
-        <v>23.07632155145449</v>
+        <v>23.07632155145448</v>
       </c>
     </row>
   </sheetData>
